--- a/quizzes/037_halloween_costume_quiz--quizzes.xlsx
+++ b/quizzes/037_halloween_costume_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C212"/>
+  <dimension ref="A1:C205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>luke_skywalker</t>
+          <t>yoda</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Luke Skywalker</t>
+          <t>Yoda</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>yoda</t>
+          <t>obi-wan_kenobi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yoda</t>
+          <t>Obi-Wan Kenobi</t>
         </is>
       </c>
     </row>
@@ -2372,46 +2372,46 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>han_solo</t>
+          <t>darth_maul</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Han Solo</t>
+          <t>Darth Maul</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>favorite_movie_character_choices</t>
+          <t>favorite_book_character_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>obi-wan_kenobi</t>
+          <t>harry_potter</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Obi-Wan Kenobi</t>
+          <t>Harry Potter</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>favorite_movie_character_choices</t>
+          <t>favorite_book_character_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>darth_maul</t>
+          <t>heirl_potter</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Darth Maul</t>
+          <t>Heirl Potter</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>harry_potter</t>
+          <t>ron_weasley</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Harry Potter</t>
+          <t>Ron Weasley</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>heirl_potter</t>
+          <t>hermione_granger</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Heirl Potter</t>
+          <t>Hermione Granger</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ron_weasley</t>
+          <t>frodo_baggins</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ron Weasley</t>
+          <t>Frodo Baggins</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>hermione_granger</t>
+          <t>samwise_gamgee</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermione Granger</t>
+          <t>Samwise Gamgee</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>frodo_baggins</t>
+          <t>gandalf</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Frodo Baggins</t>
+          <t>Gandalf</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>samwise_gamgee</t>
+          <t>bilbo_baggins</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Samwise Gamgee</t>
+          <t>Bilbo Baggins</t>
         </is>
       </c>
     </row>
@@ -2525,46 +2525,46 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>gandalf</t>
+          <t>smaegol_gloom</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gandalf</t>
+          <t>Smaegol Gloom</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>favorite_book_character_choices</t>
+          <t>favorite_game_character_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>bilbo_baggins</t>
+          <t>mario</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bilbo Baggins</t>
+          <t>Mario</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>favorite_book_character_choices</t>
+          <t>favorite_game_character_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>smaegol_gloom</t>
+          <t>link</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Smaegol Gloom</t>
+          <t>Link</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>mario</t>
+          <t>sonic_the_hedgehog</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mario</t>
+          <t>Sonic the Hedgehog</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>donkey_kng</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>Donkey Kng</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>sonic_the_hedgehog</t>
+          <t>pacman</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sonic the Hedgehog</t>
+          <t>Pacman</t>
         </is>
       </c>
     </row>
@@ -2627,97 +2627,97 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>donkey_kng</t>
+          <t>bumblebee</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Donkey Kng</t>
+          <t>Bumblebee</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>favorite_game_character_choices</t>
+          <t>favorite_game_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>pacman</t>
+          <t>minecraft</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pacman</t>
+          <t>Minecraft</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>favorite_game_character_choices</t>
+          <t>favorite_game_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>bumblebee</t>
+          <t>super_mario_bros</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bumblebee</t>
+          <t>Super Mario Bros</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>favorite_game_character_choices</t>
+          <t>favorite_game_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>the_legend_of_zelda</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>The Legend of Zelda</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>favorite_game_character_choices</t>
+          <t>favorite_game_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>mario</t>
+          <t>super_smash_bros</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mario</t>
+          <t>Super Smash Bros</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>favorite_game_character_choices</t>
+          <t>favorite_game_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>pacman</t>
+          <t>tetris</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pacman</t>
+          <t>Tetris</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>minecraft</t>
+          <t>pac-man</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minecraft</t>
+          <t>Pac-Man</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>super_mario_bros</t>
+          <t>call_of_duty</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Super Mario Bros</t>
+          <t>Call of Duty</t>
         </is>
       </c>
     </row>
@@ -2763,114 +2763,114 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>the_legend_of_zelda</t>
+          <t>assassin's_creed</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>The Legend of Zelda</t>
+          <t>Assassin's Creed</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_music_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>super_smash_bros</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Super Smash Bros</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_music_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>tetris</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tetris</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_music_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>pac-man</t>
+          <t>hip_hop</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pac-Man</t>
+          <t>Hip Hop</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_music_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>call_of_duty</t>
+          <t>jaz</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Call of Duty</t>
+          <t>Jaz</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_music_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>assassin's_creed</t>
+          <t>country</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Assassin's Creed</t>
+          <t>Country</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_music_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>the_legend_of_zelda</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>The Legend of Zelda</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rock</t>
+          <t>Electronic</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pop</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -2916,114 +2916,114 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>hip_hop</t>
+          <t>opera</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hip Hop</t>
+          <t>Opera</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>favorite_music_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jaz</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jaz</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>favorite_music_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Burger</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>favorite_music_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>classical</t>
+          <t>tacos</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Classical</t>
+          <t>Tacos</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>favorite_music_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>sushi</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Electronic</t>
+          <t>Sushi</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>favorite_music_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>ice_cream</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Ice Cream</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>favorite_music_choices</t>
+          <t>favorite_food_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>opera</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Opera</t>
+          <t>Cake</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>steak</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pizza</t>
+          <t>Steak</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>burger</t>
+          <t>fries</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Burger</t>
+          <t>Fries</t>
         </is>
       </c>
     </row>
@@ -3069,114 +3069,114 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>tacos</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>favorite_holiday_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>sushi</t>
+          <t>halloween</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sushi</t>
+          <t>Halloween</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>favorite_holiday_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ice_cream</t>
+          <t>christmas</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ice Cream</t>
+          <t>Christmas</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>favorite_holiday_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>fourth_of_july</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cake</t>
+          <t>Fourth of July</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>favorite_holiday_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>steak</t>
+          <t>thanksgiving</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>favorite_holiday_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>fries</t>
+          <t>birthday</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fries</t>
+          <t>Birthday</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>favorite_holiday_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>new_year's_eve</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>New Year's Eve</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>halloween</t>
+          <t>valentine's_day</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Halloween</t>
+          <t>Valentine's Day</t>
         </is>
       </c>
     </row>
@@ -3205,131 +3205,131 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>christmas</t>
+          <t>easter</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Easter</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>favorite_holiday_choices</t>
+          <t>favorite_activity_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>fourth_of_july</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fourth of July</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>favorite_holiday_choices</t>
+          <t>favorite_activity_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>thanksgiving</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>favorite_holiday_choices</t>
+          <t>favorite_activity_choices</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>birthday</t>
+          <t>playing_video_games</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Birthday</t>
+          <t>Playing Video Games</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>favorite_holiday_choices</t>
+          <t>favorite_activity_choices</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>new_year's_eve</t>
+          <t>singing</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New Year's Eve</t>
+          <t>Singing</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>favorite_holiday_choices</t>
+          <t>favorite_activity_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>valentine's_day</t>
+          <t>dancing</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Valentine's Day</t>
+          <t>Dancing</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>favorite_holiday_choices</t>
+          <t>favorite_activity_choices</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>easter</t>
+          <t>traveling</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Easter</t>
+          <t>Traveling</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>favorite_holiday_choices</t>
+          <t>favorite_activity_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>christmas</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
@@ -3358,131 +3358,131 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Swimming</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>favorite_activity_choices</t>
+          <t>favorite_place_choices</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>playing_video_games</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Playing Video Games</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>favorite_activity_choices</t>
+          <t>favorite_place_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>singing</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Singing</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>favorite_activity_choices</t>
+          <t>favorite_place_choices</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>dancing</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dancing</t>
+          <t>City</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>favorite_activity_choices</t>
+          <t>favorite_place_choices</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>traveling</t>
+          <t>park</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Traveling</t>
+          <t>Park</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>favorite_activity_choices</t>
+          <t>favorite_place_choices</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>writing</t>
+          <t>forest</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Writing</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>favorite_activity_choices</t>
+          <t>favorite_place_choices</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>desert</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hiking</t>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>favorite_activity_choices</t>
+          <t>favorite_place_choices</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>island</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Swimming</t>
+          <t>Island</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>beach</t>
+          <t>river</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>River</t>
         </is>
       </c>
     </row>
@@ -3511,131 +3511,131 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Lake</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>favorite_place_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>favorite_place_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>park</t>
+          <t>playing_video_games</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Playing Video Games</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>favorite_place_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>forest</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>favorite_place_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>desert</t>
+          <t>dancing</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Desert</t>
+          <t>Dancing</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>favorite_place_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>island</t>
+          <t>singing</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Island</t>
+          <t>Singing</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>favorite_place_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>favorite_place_choices</t>
+          <t>favorite_hobby_choices</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>lake</t>
+          <t>drawing</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Drawing</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3647,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
@@ -3664,131 +3664,131 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>playing_video_games</t>
+          <t>traveling</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Playing Video Games</t>
+          <t>Traveling</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>favorite_hobby_choices</t>
+          <t>favorite_language_choices</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>favorite_hobby_choices</t>
+          <t>favorite_language_choices</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>dancing</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Dancing</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>favorite_hobby_choices</t>
+          <t>favorite_language_choices</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>singing</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Singing</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>favorite_hobby_choices</t>
+          <t>favorite_language_choices</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hiking</t>
+          <t>German</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>favorite_hobby_choices</t>
+          <t>favorite_language_choices</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>drawing</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>favorite_hobby_choices</t>
+          <t>favorite_language_choices</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>writing</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Writing</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>favorite_hobby_choices</t>
+          <t>favorite_language_choices</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>traveling</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Traveling</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>portuguese</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Portuguese</t>
         </is>
       </c>
     </row>
@@ -3817,131 +3817,131 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_subject_choices</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_subject_choices</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_subject_choices</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>History</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_subject_choices</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>italian</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Italian</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_subject_choices</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>foreign_language</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Foreign Language</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_subject_choices</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>portuguese</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_subject_choices</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>arabic</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>math</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -3970,131 +3970,131 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>science</t>
+          <t>gym</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Gym</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>favorite_subject_choices</t>
+          <t>favorite_food_type_choices</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>sweets</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Sweets</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>favorite_subject_choices</t>
+          <t>favorite_food_type_choices</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>savory</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Savory</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>favorite_subject_choices</t>
+          <t>favorite_food_type_choices</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>foreign_language</t>
+          <t>salads</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Foreign Language</t>
+          <t>Salads</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>favorite_subject_choices</t>
+          <t>favorite_food_type_choices</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>soups</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>Soups</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>favorite_subject_choices</t>
+          <t>favorite_food_type_choices</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>desserts</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Desserts</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>favorite_subject_choices</t>
+          <t>favorite_food_type_choices</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>physical_education</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Physical Education</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>favorite_subject_choices</t>
+          <t>favorite_food_type_choices</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>gym</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Gym</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>sweets</t>
+          <t>proteins</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sweets</t>
+          <t>Proteins</t>
         </is>
       </c>
     </row>
@@ -4123,131 +4123,131 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>savory</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Savory</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>favorite_food_type_choices</t>
+          <t>favorite_movie_choices</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>salads</t>
+          <t>harry_potter</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Salads</t>
+          <t>Harry Potter</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>favorite_food_type_choices</t>
+          <t>favorite_movie_choices</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>soups</t>
+          <t>star_wars</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Soups</t>
+          <t>Star Wars</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>favorite_food_type_choices</t>
+          <t>favorite_movie_choices</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>desserts</t>
+          <t>the_lord_of_the_rings</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Desserts</t>
+          <t>The Lord of the Rings</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>favorite_food_type_choices</t>
+          <t>favorite_movie_choices</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>fruits</t>
+          <t>the_avengers</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>The Avengers</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>favorite_food_type_choices</t>
+          <t>favorite_movie_choices</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>vegetables</t>
+          <t>the_walking_dead</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Vegetables</t>
+          <t>The Walking Dead</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>favorite_food_type_choices</t>
+          <t>favorite_movie_choices</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>proteins</t>
+          <t>the_hunger_games</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Proteins</t>
+          <t>The Hunger Games</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>favorite_food_type_choices</t>
+          <t>favorite_movie_choices</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>grains</t>
+          <t>the_godfather</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Grains</t>
+          <t>The Godfather</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>harry_potter</t>
+          <t>the_wizard_of_oz</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Harry Potter</t>
+          <t>The Wizard of Oz</t>
         </is>
       </c>
     </row>
@@ -4276,131 +4276,131 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>star_wars</t>
+          <t>the_princess_bride</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Star Wars</t>
+          <t>The Princess Bride</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>favorite_movie_choices</t>
+          <t>favorite_book_choices</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>the_lord_of_the_rings</t>
+          <t>harry_potter</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>The Lord of the Rings</t>
+          <t>Harry Potter</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>favorite_movie_choices</t>
+          <t>favorite_book_choices</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>the_avengers</t>
+          <t>the_lord_of_the_rings</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>The Avengers</t>
+          <t>The Lord of the Rings</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>favorite_movie_choices</t>
+          <t>favorite_book_choices</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>the_walking_dead</t>
+          <t>the_hunger_games</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>The Walking Dead</t>
+          <t>The Hunger Games</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>favorite_movie_choices</t>
+          <t>favorite_book_choices</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>the_hunger_games</t>
+          <t>the_godfather</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>The Hunger Games</t>
+          <t>The Godfather</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>favorite_movie_choices</t>
+          <t>favorite_book_choices</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>the_godfather</t>
+          <t>the_wizard_of_oz</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>The Godfather</t>
+          <t>The Wizard of Oz</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>favorite_movie_choices</t>
+          <t>favorite_book_choices</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>the_wizard_of_oz</t>
+          <t>alice_in_wonderland</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>The Wizard of Oz</t>
+          <t>Alice in Wonderland</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>favorite_movie_choices</t>
+          <t>favorite_book_choices</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>the_princess_bride</t>
+          <t>the_great_gatsby</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>The Princess Bride</t>
+          <t>The Great Gatsby</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>harry_potter</t>
+          <t>the_catcher_in_the_rye</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Harry Potter</t>
+          <t>The Catcher in the Rye</t>
         </is>
       </c>
     </row>
@@ -4429,131 +4429,131 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>the_lord_of_the_rings</t>
+          <t>the_little_mermaid</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>The Lord of the Rings</t>
+          <t>The Little Mermaid</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>favorite_book_choices</t>
+          <t>favorite_game_console_choices</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>the_hunger_games</t>
+          <t>playstation</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>The Hunger Games</t>
+          <t>PlayStation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>favorite_book_choices</t>
+          <t>favorite_game_console_choices</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>the_godfather</t>
+          <t>xbox</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>The Godfather</t>
+          <t>Xbox</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>favorite_book_choices</t>
+          <t>favorite_game_console_choices</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>the_wizard_of_oz</t>
+          <t>nintendo</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>The Wizard of Oz</t>
+          <t>Nintendo</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>favorite_book_choices</t>
+          <t>favorite_game_console_choices</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>alice_in_wonderland</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Alice in Wonderland</t>
+          <t>PC</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>favorite_book_choices</t>
+          <t>favorite_game_console_choices</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>the_great_gatsby</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>The Great Gatsby</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>favorite_book_choices</t>
+          <t>favorite_game_console_choices</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>the_catcher_in_the_rye</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>The Catcher in the Rye</t>
+          <t>Switch</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>favorite_book_choices</t>
+          <t>favorite_game_console_choices</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>the_little_mermaid</t>
+          <t>wii</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>The Little Mermaid</t>
+          <t>Wii</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>playstation</t>
+          <t>psp</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>PSP</t>
         </is>
       </c>
     </row>
@@ -4582,129 +4582,10 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>xbox</t>
+          <t>gameboy</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
-        <is>
-          <t>Xbox</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>favorite_game_console_choices</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>nintendo</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Nintendo</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>favorite_game_console_choices</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>favorite_game_console_choices</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>mac</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Mac</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>favorite_game_console_choices</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Switch</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>favorite_game_console_choices</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>wii</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Wii</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>favorite_game_console_choices</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>psp</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>PSP</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>favorite_game_console_choices</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>gameboy</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
         <is>
           <t>Gameboy</t>
         </is>
